--- a/SGC-CKN/Excel/7acc4072-4e2c-4519-889e-0778b6f39da7_Thanh_Hoá_P11-09_D800_27-03-2026.xlsx
+++ b/SGC-CKN/Excel/7acc4072-4e2c-4519-889e-0778b6f39da7_Thanh_Hoá_P11-09_D800_27-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -104,6 +104,9 @@
   <si>
     <t xml:space="preserve">10:30
 27/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>3</t>
@@ -1163,24 +1166,24 @@
         <v>3.6</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-3.12</v>
@@ -1198,24 +1201,24 @@
         <v>20.4</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-13.32</v>
@@ -1233,24 +1236,24 @@
         <v>5.2</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-18.52</v>
@@ -1268,24 +1271,24 @@
         <v>10.7</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="19">
         <v>-29.22</v>
@@ -1303,24 +1306,24 @@
         <v>6.8</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="22">
         <v>-36.02</v>
@@ -1338,24 +1341,24 @@
         <v>2.5</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-38.52</v>
@@ -1373,24 +1376,24 @@
         <v>2.6</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-45.5</v>
@@ -1408,12 +1411,12 @@
         <v>1.19</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1519,31 +1522,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1583,7 +1586,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1612,7 +1615,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1641,7 +1644,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1670,7 +1673,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1699,7 +1702,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1728,7 +1731,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1757,7 +1760,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1780,13 +1783,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
